--- a/Team-Data/2008-09/11-13-2008-09.xlsx
+++ b/Team-Data/2008-09/11-13-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>7.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE2" t="n">
         <v>3</v>
@@ -748,7 +815,7 @@
         <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH2" t="n">
         <v>11</v>
@@ -757,10 +824,10 @@
         <v>11</v>
       </c>
       <c r="AJ2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK2" t="n">
         <v>12</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>13</v>
       </c>
       <c r="AL2" t="n">
         <v>2</v>
@@ -772,10 +839,10 @@
         <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
         <v>27</v>
@@ -784,37 +851,37 @@
         <v>13</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX2" t="n">
         <v>9</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7</v>
       </c>
       <c r="AY2" t="n">
         <v>20</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
         <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -843,85 +910,85 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
         <v>8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.875</v>
+        <v>0.889</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="J3" t="n">
-        <v>76.59999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="M3" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.278</v>
+        <v>0.271</v>
       </c>
       <c r="O3" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="P3" t="n">
-        <v>30.4</v>
+        <v>30.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.761</v>
+        <v>0.744</v>
       </c>
       <c r="R3" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="S3" t="n">
-        <v>34.3</v>
+        <v>33.3</v>
       </c>
       <c r="T3" t="n">
-        <v>45.8</v>
+        <v>44.7</v>
       </c>
       <c r="U3" t="n">
-        <v>20.1</v>
+        <v>19.7</v>
       </c>
       <c r="V3" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="W3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X3" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.9</v>
+        <v>24.3</v>
       </c>
       <c r="AA3" t="n">
         <v>26.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>95</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -942,13 +1009,13 @@
         <v>26</v>
       </c>
       <c r="AK3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL3" t="n">
         <v>27</v>
       </c>
       <c r="AM3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AN3" t="n">
         <v>29</v>
@@ -957,37 +1024,37 @@
         <v>3</v>
       </c>
       <c r="AP3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AR3" t="n">
         <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV3" t="n">
         <v>29</v>
       </c>
       <c r="AW3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY3" t="n">
         <v>8</v>
       </c>
-      <c r="AX3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-5.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG4" t="n">
         <v>23</v>
@@ -1124,25 +1191,25 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
         <v>21</v>
       </c>
       <c r="AM4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
         <v>14</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
         <v>16</v>
@@ -1154,19 +1221,19 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV4" t="n">
         <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX4" t="n">
         <v>24</v>
       </c>
       <c r="AY4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ4" t="n">
         <v>9</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -1225,73 +1292,73 @@
         <v>34.9</v>
       </c>
       <c r="J5" t="n">
-        <v>84.3</v>
+        <v>82.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.414</v>
+        <v>0.424</v>
       </c>
       <c r="L5" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="N5" t="n">
-        <v>0.368</v>
+        <v>0.375</v>
       </c>
       <c r="O5" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="P5" t="n">
-        <v>26.3</v>
+        <v>27.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.781</v>
+        <v>0.778</v>
       </c>
       <c r="R5" t="n">
-        <v>13.3</v>
+        <v>13.8</v>
       </c>
       <c r="S5" t="n">
-        <v>31.6</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>44.9</v>
+        <v>44.1</v>
       </c>
       <c r="U5" t="n">
-        <v>17</v>
+        <v>18.8</v>
       </c>
       <c r="V5" t="n">
-        <v>13.9</v>
+        <v>15.4</v>
       </c>
       <c r="W5" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="X5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AD5" t="n">
         <v>6</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>19</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
@@ -1303,64 +1370,64 @@
         <v>21</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN5" t="n">
         <v>11</v>
       </c>
       <c r="AO5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP5" t="n">
         <v>10</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AQ5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA5" t="n">
         <v>12</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>15</v>
-      </c>
       <c r="BB5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -1392,58 +1459,58 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>37.9</v>
+        <v>35.6</v>
       </c>
       <c r="J6" t="n">
-        <v>77.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.488</v>
+        <v>0.47</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="M6" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>0.331</v>
+        <v>0.313</v>
       </c>
       <c r="O6" t="n">
-        <v>20.9</v>
+        <v>22.6</v>
       </c>
       <c r="P6" t="n">
-        <v>26.6</v>
+        <v>29.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.784</v>
+        <v>0.774</v>
       </c>
       <c r="R6" t="n">
         <v>10.5</v>
       </c>
       <c r="S6" t="n">
-        <v>29</v>
+        <v>29.9</v>
       </c>
       <c r="T6" t="n">
-        <v>39.5</v>
+        <v>40.4</v>
       </c>
       <c r="U6" t="n">
-        <v>21.3</v>
+        <v>19.5</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>14.6</v>
       </c>
       <c r="W6" t="n">
         <v>7.8</v>
@@ -1452,97 +1519,97 @@
         <v>6.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.5</v>
+        <v>22.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.8</v>
+        <v>23</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.6</v>
+        <v>99.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH6" t="n">
         <v>11</v>
       </c>
       <c r="AI6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK6" t="n">
         <v>4</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3</v>
-      </c>
       <c r="AL6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AM6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
         <v>22</v>
       </c>
       <c r="AS6" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AT6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC6" t="n">
         <v>4</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -1571,151 +1638,151 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.25</v>
+        <v>0.286</v>
       </c>
       <c r="H7" t="n">
         <v>48</v>
       </c>
       <c r="I7" t="n">
-        <v>35.9</v>
+        <v>36.4</v>
       </c>
       <c r="J7" t="n">
-        <v>84.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="K7" t="n">
-        <v>0.425</v>
+        <v>0.434</v>
       </c>
       <c r="L7" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="M7" t="n">
-        <v>19.3</v>
+        <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.292</v>
+        <v>0.295</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>17.3</v>
       </c>
       <c r="P7" t="n">
-        <v>22.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.791</v>
+        <v>0.796</v>
       </c>
       <c r="R7" t="n">
-        <v>12.4</v>
+        <v>11.9</v>
       </c>
       <c r="S7" t="n">
-        <v>32.6</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>45</v>
+        <v>43.7</v>
       </c>
       <c r="U7" t="n">
-        <v>19.9</v>
+        <v>20.6</v>
       </c>
       <c r="V7" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W7" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="X7" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="Y7" t="n">
         <v>4.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.8</v>
+        <v>19.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>95.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.8</v>
+        <v>-3.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AH7" t="n">
         <v>11</v>
       </c>
       <c r="AI7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
         <v>5</v>
       </c>
       <c r="AK7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT7" t="n">
         <v>9</v>
       </c>
-      <c r="AN7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO7" t="n">
+      <c r="AU7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX7" t="n">
         <v>22</v>
       </c>
-      <c r="AP7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AV7" t="n">
+      <c r="AY7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>9</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>10</v>
       </c>
       <c r="BA7" t="n">
         <v>26</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -1753,160 +1820,160 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="H8" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I8" t="n">
         <v>35.1</v>
       </c>
       <c r="J8" t="n">
-        <v>79.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.442</v>
+        <v>0.437</v>
       </c>
       <c r="L8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.288</v>
+        <v>0.264</v>
       </c>
       <c r="O8" t="n">
-        <v>25.3</v>
+        <v>25.9</v>
       </c>
       <c r="P8" t="n">
-        <v>32.5</v>
+        <v>33.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.777</v>
+        <v>0.767</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="S8" t="n">
-        <v>33.1</v>
+        <v>34.3</v>
       </c>
       <c r="T8" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="U8" t="n">
-        <v>21</v>
+        <v>21.7</v>
       </c>
       <c r="V8" t="n">
-        <v>16.6</v>
+        <v>17</v>
       </c>
       <c r="W8" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="X8" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>23.5</v>
+        <v>24.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>25.1</v>
+        <v>25.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1</v>
+        <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
       </c>
       <c r="AF8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>14</v>
       </c>
-      <c r="AG8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>17</v>
-      </c>
       <c r="AK8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AL8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AM8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
       </c>
       <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW8" t="n">
         <v>3</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4</v>
-      </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA8" t="n">
         <v>3</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -1935,103 +2002,103 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>36</v>
+        <v>35.6</v>
       </c>
       <c r="J9" t="n">
-        <v>81.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.442</v>
+        <v>0.44</v>
       </c>
       <c r="L9" t="n">
         <v>6.3</v>
       </c>
       <c r="M9" t="n">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.397</v>
+        <v>0.389</v>
       </c>
       <c r="O9" t="n">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="P9" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.795</v>
+        <v>0.804</v>
       </c>
       <c r="R9" t="n">
         <v>13</v>
       </c>
       <c r="S9" t="n">
-        <v>30.1</v>
+        <v>29.3</v>
       </c>
       <c r="T9" t="n">
-        <v>43.1</v>
+        <v>42.3</v>
       </c>
       <c r="U9" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="V9" t="n">
-        <v>12.5</v>
+        <v>11.7</v>
       </c>
       <c r="W9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="X9" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="Y9" t="n">
         <v>3.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.3</v>
+        <v>21.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>99.59999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AF9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH9" t="n">
         <v>11</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK9" t="n">
         <v>18</v>
@@ -2043,52 +2110,52 @@
         <v>19</v>
       </c>
       <c r="AN9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR9" t="n">
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AU9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AV9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX9" t="n">
         <v>4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>5</v>
       </c>
       <c r="AY9" t="n">
         <v>6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC9" t="n">
         <v>9</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>8</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -2117,70 +2184,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="H10" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="I10" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J10" t="n">
-        <v>87.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.426</v>
+        <v>0.428</v>
       </c>
       <c r="L10" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="M10" t="n">
-        <v>17.9</v>
+        <v>19</v>
       </c>
       <c r="N10" t="n">
-        <v>0.286</v>
+        <v>0.296</v>
       </c>
       <c r="O10" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="P10" t="n">
-        <v>32.9</v>
+        <v>32.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.699</v>
+        <v>0.695</v>
       </c>
       <c r="R10" t="n">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="S10" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="T10" t="n">
-        <v>45.1</v>
+        <v>44.4</v>
       </c>
       <c r="U10" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="V10" t="n">
         <v>15.1</v>
       </c>
       <c r="W10" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="X10" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="Z10" t="n">
         <v>23</v>
@@ -2192,25 +2259,25 @@
         <v>102.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.9</v>
+        <v>-2.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>19</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH10" t="n">
         <v>3</v>
       </c>
       <c r="AI10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AJ10" t="n">
         <v>2</v>
@@ -2219,55 +2286,55 @@
         <v>24</v>
       </c>
       <c r="AL10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AM10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AO10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP10" t="n">
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR10" t="n">
         <v>1</v>
       </c>
       <c r="AS10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV10" t="n">
         <v>17</v>
       </c>
-      <c r="AT10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>18</v>
-      </c>
       <c r="AW10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX10" t="n">
         <v>2</v>
       </c>
       <c r="AY10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA10" t="n">
         <v>1</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -2377,16 +2444,16 @@
         <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG11" t="n">
         <v>8</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>9</v>
       </c>
       <c r="AH11" t="n">
         <v>6</v>
@@ -2398,10 +2465,10 @@
         <v>13</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM11" t="n">
         <v>13</v>
@@ -2413,7 +2480,7 @@
         <v>12</v>
       </c>
       <c r="AP11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
         <v>1</v>
@@ -2425,22 +2492,22 @@
         <v>9</v>
       </c>
       <c r="AT11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV11" t="n">
         <v>5</v>
       </c>
       <c r="AW11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX11" t="n">
         <v>27</v>
       </c>
       <c r="AY11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -2559,13 +2626,13 @@
         <v>4.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE12" t="n">
         <v>12</v>
       </c>
       <c r="AF12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
@@ -2574,10 +2641,10 @@
         <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK12" t="n">
         <v>6</v>
@@ -2592,25 +2659,25 @@
         <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR12" t="n">
         <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
         <v>22</v>
@@ -2619,19 +2686,19 @@
         <v>5</v>
       </c>
       <c r="AX12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-13.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
@@ -2759,13 +2826,13 @@
         <v>28</v>
       </c>
       <c r="AJ13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM13" t="n">
         <v>13</v>
@@ -2777,10 +2844,10 @@
         <v>28</v>
       </c>
       <c r="AP13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR13" t="n">
         <v>17</v>
@@ -2789,7 +2856,7 @@
         <v>25</v>
       </c>
       <c r="AT13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -2845,10 +2912,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2860,73 +2927,73 @@
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J14" t="n">
-        <v>84</v>
+        <v>83.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.442</v>
+        <v>0.446</v>
       </c>
       <c r="L14" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>17.3</v>
+        <v>16.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.394</v>
+        <v>0.421</v>
       </c>
       <c r="O14" t="n">
-        <v>25</v>
+        <v>23.6</v>
       </c>
       <c r="P14" t="n">
-        <v>33</v>
+        <v>30.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.758</v>
+        <v>0.764</v>
       </c>
       <c r="R14" t="n">
-        <v>14.5</v>
+        <v>13.7</v>
       </c>
       <c r="S14" t="n">
-        <v>34.8</v>
+        <v>35.6</v>
       </c>
       <c r="T14" t="n">
         <v>49.3</v>
       </c>
       <c r="U14" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="V14" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W14" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>24.3</v>
+        <v>23.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.2</v>
+        <v>104.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="AD14" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>1</v>
@@ -2938,34 +3005,34 @@
         <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL14" t="n">
         <v>10</v>
       </c>
       <c r="AM14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AN14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="n">
         <v>2</v>
       </c>
       <c r="AP14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2974,25 +3041,25 @@
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -3111,10 +3178,10 @@
         <v>19</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH15" t="n">
         <v>11</v>
@@ -3126,10 +3193,10 @@
         <v>23</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AM15" t="n">
         <v>26</v>
@@ -3144,16 +3211,16 @@
         <v>11</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
         <v>17</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
@@ -3162,16 +3229,16 @@
         <v>26</v>
       </c>
       <c r="AW15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>18</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>17</v>
       </c>
       <c r="BA15" t="n">
         <v>16</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -3287,25 +3354,25 @@
         <v>4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE16" t="n">
         <v>12</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH16" t="n">
         <v>11</v>
       </c>
       <c r="AI16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3317,19 +3384,19 @@
         <v>6</v>
       </c>
       <c r="AN16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AP16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS16" t="n">
         <v>28</v>
@@ -3338,7 +3405,7 @@
         <v>28</v>
       </c>
       <c r="AU16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV16" t="n">
         <v>5</v>
@@ -3347,19 +3414,19 @@
         <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ16" t="n">
         <v>8</v>
       </c>
       <c r="BA16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC16" t="n">
         <v>8</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -3391,160 +3458,160 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
       </c>
       <c r="I17" t="n">
-        <v>35.1</v>
+        <v>35.3</v>
       </c>
       <c r="J17" t="n">
-        <v>80.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.434</v>
+        <v>0.439</v>
       </c>
       <c r="L17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.358</v>
+        <v>0.366</v>
       </c>
       <c r="O17" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="P17" t="n">
-        <v>25.9</v>
+        <v>25.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.725</v>
+        <v>0.727</v>
       </c>
       <c r="R17" t="n">
         <v>12.4</v>
       </c>
       <c r="S17" t="n">
-        <v>31.4</v>
+        <v>30</v>
       </c>
       <c r="T17" t="n">
-        <v>43.8</v>
+        <v>42.4</v>
       </c>
       <c r="U17" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V17" t="n">
-        <v>15.9</v>
+        <v>16.2</v>
       </c>
       <c r="W17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="X17" t="n">
         <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.8</v>
+        <v>25.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>93.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1</v>
+        <v>-1.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>12</v>
       </c>
       <c r="AF17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AI17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK17" t="n">
         <v>19</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>20</v>
-      </c>
       <c r="AL17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM17" t="n">
         <v>27</v>
       </c>
       <c r="AN17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP17" t="n">
         <v>14</v>
       </c>
-      <c r="AO17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>13</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR17" t="n">
         <v>8</v>
       </c>
       <c r="AS17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT17" t="n">
         <v>14</v>
       </c>
-      <c r="AT17" t="n">
-        <v>9</v>
-      </c>
       <c r="AU17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
         <v>23</v>
       </c>
       <c r="AW17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX17" t="n">
         <v>28</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ17" t="n">
         <v>29</v>
       </c>
       <c r="BA17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB17" t="n">
         <v>24</v>
       </c>
       <c r="BC17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-4.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="n">
         <v>27</v>
       </c>
       <c r="AF18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG18" t="n">
         <v>28</v>
@@ -3672,19 +3739,19 @@
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
         <v>24</v>
       </c>
       <c r="AM18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO18" t="n">
         <v>18</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>20</v>
       </c>
       <c r="AP18" t="n">
         <v>23</v>
@@ -3705,25 +3772,25 @@
         <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW18" t="n">
         <v>24</v>
       </c>
       <c r="AX18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA18" t="n">
         <v>22</v>
       </c>
-      <c r="AY18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>23</v>
-      </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC18" t="n">
         <v>23</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>-7.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE19" t="n">
         <v>23</v>
       </c>
       <c r="AF19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG19" t="n">
         <v>23</v>
@@ -3854,7 +3921,7 @@
         <v>22</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
         <v>9</v>
@@ -3866,34 +3933,34 @@
         <v>16</v>
       </c>
       <c r="AO19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP19" t="n">
         <v>19</v>
       </c>
-      <c r="AP19" t="n">
-        <v>20</v>
-      </c>
       <c r="AQ19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AR19" t="n">
         <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT19" t="n">
         <v>18</v>
       </c>
       <c r="AU19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW19" t="n">
         <v>24</v>
       </c>
       <c r="AX19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY19" t="n">
         <v>18</v>
@@ -3902,7 +3969,7 @@
         <v>30</v>
       </c>
       <c r="BA19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB19" t="n">
         <v>27</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -4015,13 +4082,13 @@
         <v>3.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
         <v>12</v>
       </c>
       <c r="AF20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG20" t="n">
         <v>12</v>
@@ -4033,10 +4100,10 @@
         <v>22</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
         <v>3</v>
@@ -4045,16 +4112,16 @@
         <v>4</v>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO20" t="n">
         <v>22</v>
       </c>
       <c r="AP20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR20" t="n">
         <v>27</v>
@@ -4063,31 +4130,31 @@
         <v>21</v>
       </c>
       <c r="AT20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU20" t="n">
         <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="n">
         <v>25</v>
       </c>
       <c r="AY20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ20" t="n">
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -4197,16 +4264,16 @@
         <v>0.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG21" t="n">
         <v>8</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>9</v>
       </c>
       <c r="AH21" t="n">
         <v>11</v>
@@ -4218,7 +4285,7 @@
         <v>3</v>
       </c>
       <c r="AK21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO21" t="n">
         <v>28</v>
@@ -4236,31 +4303,31 @@
         <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS21" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AT21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU21" t="n">
         <v>4</v>
       </c>
       <c r="AV21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
         <v>7</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4409,25 +4476,25 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP22" t="n">
         <v>22</v>
       </c>
       <c r="AQ22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR22" t="n">
         <v>6</v>
       </c>
       <c r="AS22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
         <v>29</v>
@@ -4439,13 +4506,13 @@
         <v>20</v>
       </c>
       <c r="AX22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA22" t="n">
         <v>27</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -4561,37 +4628,37 @@
         <v>6.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG23" t="n">
         <v>8</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>9</v>
       </c>
       <c r="AH23" t="n">
         <v>11</v>
       </c>
       <c r="AI23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM23" t="n">
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO23" t="n">
         <v>11</v>
@@ -4603,37 +4670,37 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS23" t="n">
         <v>5</v>
       </c>
       <c r="AT23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
         <v>1</v>
       </c>
       <c r="AY23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BB23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BC23" t="n">
         <v>5</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -4743,13 +4810,13 @@
         <v>1.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
         <v>19</v>
       </c>
       <c r="AF24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG24" t="n">
         <v>19</v>
@@ -4758,16 +4825,16 @@
         <v>11</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ24" t="n">
         <v>8</v>
       </c>
       <c r="AK24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM24" t="n">
         <v>28</v>
@@ -4779,13 +4846,13 @@
         <v>27</v>
       </c>
       <c r="AP24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AR24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS24" t="n">
         <v>3</v>
@@ -4794,7 +4861,7 @@
         <v>2</v>
       </c>
       <c r="AU24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4815,10 +4882,10 @@
         <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -4931,16 +4998,16 @@
         <v>3</v>
       </c>
       <c r="AF25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH25" t="n">
         <v>11</v>
       </c>
       <c r="AI25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ25" t="n">
         <v>30</v>
@@ -4952,7 +5019,7 @@
         <v>12</v>
       </c>
       <c r="AM25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN25" t="n">
         <v>10</v>
@@ -4961,43 +5028,43 @@
         <v>5</v>
       </c>
       <c r="AP25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR25" t="n">
         <v>30</v>
       </c>
       <c r="AS25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU25" t="n">
         <v>14</v>
       </c>
       <c r="AV25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW25" t="n">
         <v>24</v>
       </c>
       <c r="AX25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY25" t="n">
         <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA25" t="n">
         <v>10</v>
       </c>
       <c r="BB25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC25" t="n">
         <v>11</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -5029,109 +5096,109 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
         <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>0.714</v>
+        <v>0.625</v>
       </c>
       <c r="H26" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>36.3</v>
+        <v>35.4</v>
       </c>
       <c r="J26" t="n">
-        <v>79.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="K26" t="n">
-        <v>0.457</v>
+        <v>0.442</v>
       </c>
       <c r="L26" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="M26" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.406</v>
+        <v>0.408</v>
       </c>
       <c r="O26" t="n">
-        <v>19.7</v>
+        <v>18.3</v>
       </c>
       <c r="P26" t="n">
-        <v>25</v>
+        <v>23.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.789</v>
+        <v>0.772</v>
       </c>
       <c r="R26" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S26" t="n">
-        <v>25.9</v>
+        <v>26.5</v>
       </c>
       <c r="T26" t="n">
-        <v>38.1</v>
+        <v>38.9</v>
       </c>
       <c r="U26" t="n">
         <v>19.4</v>
       </c>
       <c r="V26" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="W26" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="X26" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.6</v>
+        <v>-2</v>
       </c>
       <c r="AD26" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG26" t="n">
         <v>8</v>
       </c>
-      <c r="AF26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>7</v>
-      </c>
       <c r="AH26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI26" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AJ26" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM26" t="n">
         <v>10</v>
@@ -5140,22 +5207,22 @@
         <v>5</v>
       </c>
       <c r="AO26" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AR26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS26" t="n">
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU26" t="n">
         <v>20</v>
@@ -5167,22 +5234,22 @@
         <v>17</v>
       </c>
       <c r="AX26" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AY26" t="n">
         <v>1</v>
       </c>
       <c r="AZ26" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC26" t="n">
         <v>19</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>14</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -5295,10 +5362,10 @@
         <v>12</v>
       </c>
       <c r="AF27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH27" t="n">
         <v>11</v>
@@ -5319,16 +5386,16 @@
         <v>24</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
         <v>26</v>
@@ -5340,10 +5407,10 @@
         <v>25</v>
       </c>
       <c r="AU27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW27" t="n">
         <v>28</v>
@@ -5355,13 +5422,13 @@
         <v>21</v>
       </c>
       <c r="AZ27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
         <v>18</v>
       </c>
       <c r="BB27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BC27" t="n">
         <v>24</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -5471,13 +5538,13 @@
         <v>-3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
         <v>23</v>
       </c>
       <c r="AF28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG28" t="n">
         <v>23</v>
@@ -5486,10 +5553,10 @@
         <v>2</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
         <v>5</v>
@@ -5498,7 +5565,7 @@
         <v>6</v>
       </c>
       <c r="AM28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN28" t="n">
         <v>9</v>
@@ -5522,7 +5589,7 @@
         <v>19</v>
       </c>
       <c r="AU28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
@@ -5534,7 +5601,7 @@
         <v>29</v>
       </c>
       <c r="AY28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ28" t="n">
         <v>6</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>-1.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
       </c>
       <c r="AF29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH29" t="n">
         <v>6</v>
@@ -5680,13 +5747,13 @@
         <v>11</v>
       </c>
       <c r="AM29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP29" t="n">
         <v>24</v>
@@ -5698,7 +5765,7 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT29" t="n">
         <v>30</v>
@@ -5713,10 +5780,10 @@
         <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ29" t="n">
         <v>2</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -5835,28 +5902,28 @@
         <v>6.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
         <v>3</v>
       </c>
       <c r="AF30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH30" t="n">
         <v>11</v>
       </c>
       <c r="AI30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ30" t="n">
         <v>21</v>
       </c>
       <c r="AK30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL30" t="n">
         <v>29</v>
@@ -5868,28 +5935,28 @@
         <v>24</v>
       </c>
       <c r="AO30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>18</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>17</v>
-      </c>
       <c r="AR30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AT30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
         <v>6</v>
@@ -5901,16 +5968,16 @@
         <v>28</v>
       </c>
       <c r="AZ30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE31" t="n">
         <v>27</v>
       </c>
       <c r="AF31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG31" t="n">
         <v>27</v>
@@ -6032,31 +6099,31 @@
         <v>4</v>
       </c>
       <c r="AI31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
       </c>
       <c r="AM31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN31" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR31" t="n">
         <v>21</v>
@@ -6068,16 +6135,16 @@
         <v>24</v>
       </c>
       <c r="AU31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW31" t="n">
         <v>16</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="AX31" t="n">
         <v>15</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>17</v>
       </c>
       <c r="AY31" t="n">
         <v>19</v>
@@ -6089,7 +6156,7 @@
         <v>4</v>
       </c>
       <c r="BB31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-13-2008-09</t>
+          <t>2008-11-13</t>
         </is>
       </c>
     </row>
